--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487434_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487434_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8293</v>
+        <v>5.0517</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9262</v>
+        <v>1.0842</v>
       </c>
       <c r="F2" t="n">
-        <v>4.9031</v>
+        <v>3.9675</v>
       </c>
       <c r="G2" t="n">
         <v>3.3786</v>
@@ -610,13 +610,13 @@
         <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0751</v>
+        <v>0.2975</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8667</v>
+        <v>0.0247</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2083</v>
+        <v>0.2728</v>
       </c>
       <c r="V2" t="n">
         <v>1.7673</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5071</v>
+        <v>4.0013</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3767</v>
+        <v>0.6837</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1304</v>
+        <v>3.3176</v>
       </c>
       <c r="G3" t="n">
         <v>2.8873</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6555</v>
+        <v>-1.1614</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3068</v>
+        <v>-0.9998</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3487</v>
+        <v>-0.1616</v>
       </c>
       <c r="V3" t="n">
         <v>1.492</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0457</v>
+        <v>3.1564</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3832</v>
+        <v>0.8949</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6625</v>
+        <v>2.2615</v>
       </c>
       <c r="G4" t="n">
         <v>2.279</v>
@@ -766,13 +766,13 @@
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.4936</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1286</v>
+        <v>-0.617</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5243</v>
+        <v>0.1234</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9668</v>
+        <v>1.5575</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4105</v>
+        <v>1.0011</v>
       </c>
       <c r="F5" t="n">
         <v>0.5564</v>
@@ -844,10 +844,10 @@
         <v>2.546</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8604000000000001</v>
+        <v>-1.2698</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6552</v>
+        <v>-1.0645</v>
       </c>
       <c r="U5" t="n">
         <v>-0.2052</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.358</v>
+        <v>1.0777</v>
       </c>
       <c r="E6" t="n">
-        <v>1.504</v>
+        <v>1.1969</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.146</v>
+        <v>-0.1193</v>
       </c>
       <c r="G6" t="n">
         <v>1.2062</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4272</v>
+        <v>0.1469</v>
       </c>
       <c r="T6" t="n">
-        <v>0.504</v>
+        <v>0.197</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0769</v>
+        <v>-0.0501</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2754</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4708</v>
+        <v>-1.6383</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.8831</v>
+        <v>-4.3714</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4123</v>
+        <v>2.7331</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2358</v>
@@ -1078,13 +1078,13 @@
         <v>1.7626</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.3145</v>
+        <v>-1.4821</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.7227</v>
+        <v>-1.211</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5919</v>
+        <v>-0.2711</v>
       </c>
       <c r="V8" t="n">
         <v>0.2754</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6262</v>
+        <v>-2.0786</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.893</v>
+        <v>-1.586</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7333</v>
+        <v>-0.4927</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2167</v>
@@ -1156,13 +1156,13 @@
         <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9971</v>
+        <v>-0.4495</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4752</v>
+        <v>-0.1682</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5219</v>
+        <v>-0.2813</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2166</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1693</v>
+        <v>-2.417</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9258</v>
+        <v>-1.4141</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2435</v>
+        <v>-1.0029</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3086</v>
@@ -1234,13 +1234,13 @@
         <v>0.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4482</v>
+        <v>-0.6959</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.891</v>
+        <v>-0.3794</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5571</v>
+        <v>-0.3166</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2166</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.934</v>
+        <v>-5.2039</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.7403</v>
+        <v>-7.331</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8063</v>
+        <v>2.1271</v>
       </c>
       <c r="G11" t="n">
         <v>-6.2448</v>
@@ -1312,13 +1312,13 @@
         <v>2.1543</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3563</v>
+        <v>-1.6262</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.7227</v>
+        <v>-1.3133</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6337</v>
+        <v>-0.3129</v>
       </c>
       <c r="V11" t="n">
         <v>1.492</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.643000000000002</v>
+        <v>3.643200000000003</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.8416</v>
+        <v>-9.841700000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>13.4846</v>
+        <v>13.4847</v>
       </c>
       <c r="G12" t="n">
         <v>6.3955</v>
@@ -1390,13 +1390,13 @@
         <v>12.73</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.734</v>
+        <v>-6.7341</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.531499999999999</v>
+        <v>-5.5315</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2028</v>
+        <v>-1.2026</v>
       </c>
       <c r="V12" t="n">
         <v>1.0439</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4655</v>
+        <v>1.6154</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2656</v>
+        <v>-1.982</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7311</v>
+        <v>3.5974</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3573</v>
@@ -1468,13 +1468,13 @@
         <v>1.9585</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7651</v>
+        <v>1.9151</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2968</v>
+        <v>0.5805</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4683</v>
+        <v>1.3346</v>
       </c>
       <c r="V13" t="n">
         <v>1.2742</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7976</v>
+        <v>1.0361</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4567</v>
+        <v>0.1497</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3408</v>
+        <v>0.8864</v>
       </c>
       <c r="G14" t="n">
         <v>0.4149</v>
@@ -1546,13 +1546,13 @@
         <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9702</v>
+        <v>1.2088</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7399</v>
+        <v>0.4329</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2303</v>
+        <v>0.7759</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.499</v>
+        <v>0.5746</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4429</v>
+        <v>-0.3406</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9152</v>
       </c>
       <c r="G15" t="n">
         <v>0.7885</v>
@@ -1624,13 +1624,13 @@
         <v>0.1958</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1719</v>
+        <v>-0.0963</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1782</v>
+        <v>-0.0759</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0063</v>
+        <v>-0.0204</v>
       </c>
       <c r="V15" t="n">
         <v>0.6659</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1079</v>
+        <v>-0.0838</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0527</v>
+        <v>0.0496</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1606</v>
+        <v>-0.1334</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3319</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4398</v>
+        <v>0.248</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5586</v>
+        <v>0.2645</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. RUMSHA</t>
+          <t>M. RODRIGUEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4283</v>
+        <v>-0.2598</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2683</v>
+        <v>-1.6443</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1599</v>
+        <v>1.3845</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1301</v>
+        <v>1.3388</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5286999999999999</v>
+        <v>1.6417</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3986</v>
+        <v>-0.3029</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6468</v>
+        <v>1.04</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5256</v>
+        <v>2.3188</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1212</v>
+        <v>-1.2788</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5167</v>
+        <v>0.2989</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0031</v>
+        <v>-0.677</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5198</v>
+        <v>0.9759</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7834</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1751</v>
+        <v>-2.1543</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3917</v>
+        <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>0.225</v>
+        <v>-0.0687</v>
       </c>
       <c r="T17" t="n">
-        <v>0.26</v>
+        <v>-0.5299</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0349</v>
+        <v>0.4613</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CASAIS ROMERO</t>
+          <t>G. RUMSHA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4228</v>
+        <v>-0.4145</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1017</v>
+        <v>-0.5753</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5245</v>
+        <v>0.1608</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0711</v>
+        <v>0.1301</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0462</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0248</v>
+        <v>-0.3986</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1855</v>
+        <v>0.6468</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1192</v>
+        <v>0.5256</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0664</v>
+        <v>0.1212</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1144</v>
+        <v>-0.5167</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0031</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0415</v>
+        <v>-0.5198</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1751</v>
+        <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8061</v>
+        <v>0.2388</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9116</v>
+        <v>-0.0471</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1055</v>
+        <v>0.2858</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.1578</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.7086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ ALVAREZ</t>
+          <t>A. CASAIS ROMERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5864</v>
+        <v>-1.2441</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.463</v>
+        <v>-0.3076</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8766</v>
+        <v>-0.9365</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3388</v>
+        <v>-0.0711</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6417</v>
+        <v>-0.0462</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3029</v>
+        <v>-0.0248</v>
       </c>
       <c r="J19" t="n">
-        <v>1.04</v>
+        <v>-0.1855</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3188</v>
+        <v>-0.1192</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2788</v>
+        <v>-0.0664</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2989</v>
+        <v>0.1144</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.677</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9759</v>
+        <v>0.0415</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1543</v>
+        <v>-1.1751</v>
       </c>
       <c r="R19" t="n">
         <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3952</v>
+        <v>0.9848</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3486</v>
+        <v>0.5023</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0466</v>
+        <v>0.4826</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5507</v>
+        <v>-2.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5507</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9647</v>
+        <v>-2.2542</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6703</v>
+        <v>-2.7726</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7056</v>
+        <v>0.5185</v>
       </c>
       <c r="G20" t="n">
         <v>-3.4612</v>
@@ -2014,13 +2014,13 @@
         <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4597</v>
+        <v>1.1702</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5087</v>
+        <v>0.4064</v>
       </c>
       <c r="U20" t="n">
-        <v>0.951</v>
+        <v>0.7638</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5507</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1108</v>
+        <v>-2.6129</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.8802</v>
+        <v>-6.0615</v>
       </c>
       <c r="F21" t="n">
-        <v>3.7694</v>
+        <v>3.4486</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8465</v>
@@ -2092,13 +2092,13 @@
         <v>1.9585</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6354</v>
+        <v>1.1333</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8687</v>
+        <v>-0.05</v>
       </c>
       <c r="U21" t="n">
-        <v>1.5041</v>
+        <v>1.1833</v>
       </c>
       <c r="V21" t="n">
         <v>0.2754</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.643000000000001</v>
+        <v>-3.6432</v>
       </c>
       <c r="E22" t="n">
         <v>-13.4846</v>
       </c>
       <c r="F22" t="n">
-        <v>9.841699999999999</v>
+        <v>9.8415</v>
       </c>
       <c r="G22" t="n">
         <v>-6.3957</v>
@@ -2170,13 +2170,13 @@
         <v>9.792400000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>6.7342</v>
+        <v>6.734</v>
       </c>
       <c r="T22" t="n">
         <v>1.2027</v>
       </c>
       <c r="U22" t="n">
-        <v>5.5316</v>
+        <v>5.531400000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0437</v>
